--- a/Pruebas calificadas/COLEGIO TORQUIGUA-701_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO TORQUIGUA-701_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIQUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -2337,7 +2309,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -2590,7 +2558,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -2843,7 +2807,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3084,11 +3048,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -3096,7 +3056,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3325,11 +3285,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -3337,7 +3293,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIQUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3578,11 +3534,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -3590,7 +3542,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIQUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3831,11 +3783,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -3843,7 +3791,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4084,11 +4032,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -4096,7 +4040,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4337,11 +4281,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -4349,7 +4289,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4590,11 +4530,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -4602,7 +4538,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4843,11 +4779,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -4855,7 +4787,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5096,11 +5028,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -5108,7 +5036,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5349,11 +5277,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -5361,7 +5285,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5602,11 +5526,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -5614,7 +5534,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5855,11 +5775,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -5867,7 +5783,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6108,11 +6024,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -6120,7 +6032,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6361,11 +6273,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -6373,7 +6281,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6614,11 +6522,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -6626,7 +6530,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6867,11 +6771,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -6879,7 +6779,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7120,11 +7020,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -7132,7 +7028,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7373,11 +7269,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -7385,7 +7277,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7626,11 +7518,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -7638,7 +7526,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIQUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7879,11 +7767,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -7891,7 +7775,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8132,11 +8016,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -8144,7 +8024,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8385,11 +8265,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -8397,7 +8273,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8638,11 +8514,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -8650,7 +8522,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8887,11 +8759,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -8899,7 +8767,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9132,11 +9000,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -9144,7 +9008,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9385,11 +9249,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -9397,7 +9257,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9638,11 +9498,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -9650,7 +9506,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9891,11 +9747,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -9903,7 +9755,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIQUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10144,11 +9996,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -10156,7 +10004,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10397,11 +10245,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -10409,7 +10253,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10646,11 +10490,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -10658,7 +10498,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10899,11 +10739,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -10911,7 +10747,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11152,11 +10988,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -11164,7 +10996,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11405,11 +11237,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -11417,7 +11245,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11658,11 +11486,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -11670,7 +11494,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11911,11 +11735,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -11923,7 +11743,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12164,11 +11984,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -12176,7 +11992,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIQUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12417,11 +12233,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -12429,7 +12241,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIQUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12670,11 +12482,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -12682,7 +12490,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12923,11 +12731,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -12935,7 +12739,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13176,11 +12980,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -13188,7 +12988,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13429,11 +13229,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -13441,7 +13237,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIQUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13682,11 +13478,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -13694,7 +13486,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13935,11 +13727,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -13947,7 +13735,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14188,11 +13976,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -14200,7 +13984,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14441,11 +14225,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -14453,7 +14233,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14694,11 +14474,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -14706,7 +14482,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14947,11 +14723,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -14959,7 +14731,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15200,11 +14972,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -15212,7 +14980,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15453,11 +15221,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -15465,7 +15229,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIQUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15706,11 +15470,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -15718,7 +15478,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIQUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15959,11 +15719,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -15971,7 +15727,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16212,11 +15968,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -16224,7 +15976,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16465,11 +16217,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -16477,7 +16225,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16718,11 +16466,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -16730,7 +16474,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16971,11 +16715,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -16983,7 +16723,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17224,11 +16964,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -17236,7 +16972,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17477,11 +17213,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -17489,7 +17221,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17730,11 +17462,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -17742,7 +17470,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -17983,11 +17711,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -17995,7 +17719,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18236,11 +17960,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -18248,7 +17968,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -18489,11 +18209,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -18501,7 +18217,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIQUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -18742,11 +18458,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -18754,7 +18466,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -18995,11 +18707,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -19007,7 +18715,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -19244,11 +18952,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -19256,7 +18960,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIQUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -19497,11 +19201,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -19509,7 +19209,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -19750,11 +19450,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -19762,7 +19458,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -20003,11 +19699,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -20015,7 +19707,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIQUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -20256,11 +19948,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -20268,7 +19956,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -20509,11 +20197,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -20521,7 +20205,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -20762,11 +20446,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="inlineStr"/>
       <c r="B81" s="2" t="inlineStr">
         <is>
           <t>111001098931</t>
@@ -20774,7 +20454,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO TORQUIGUA (IED)</t>
+          <t>COLEGIO TORQUIGUA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
